--- a/data/trans_orig/IP38F_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP38F_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9986</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3326</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5258</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>91,54%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>63,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4794</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3376</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5153</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>93,03%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>65,51%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>11128</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>30</t>
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15941</t>
+          <t>14780</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13570</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16386</t>
+          <t>15139</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1932</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>8,46%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1780</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>6,97%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>36,75%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>34,55%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1817</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>2816</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9986</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9986</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9986</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5258</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5258</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5258</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11128</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11128</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11128</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>16386</t>
+          <t>15139</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16386</t>
+          <t>15139</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16386</t>
+          <t>15139</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,74 +1063,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13708</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11479</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14021</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>81,87%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12364</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>12274</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>14471</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>12529</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>14852</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>97,43%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>84,36%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>40</t>
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>26835</t>
+          <t>25982</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25203</t>
+          <t>24492</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27216</t>
+          <t>26295</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1176,107 +1176,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>18,13%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2323</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>15,64%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14021</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>14021</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>14021</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>12364</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>12364</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>12364</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>27216</t>
+          <t>26295</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>27216</t>
+          <t>26295</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27216</t>
+          <t>26295</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4600</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1961</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5887</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>78,14%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>33,31%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7806</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4528</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10050</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>74,04%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>42,95%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12598</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>6764</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15373</t>
+          <t>12599</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>89,05%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1287</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3926</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>21,86%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>66,69%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2737</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6015</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>25,96%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>57,05%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>834</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8221</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>52,19%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5887</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5887</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5887</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>10543</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>10543</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10543</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>16743</t>
+          <t>14148</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16743</t>
+          <t>14148</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16743</t>
+          <t>14148</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,74 +1749,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>12467</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9913</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13713</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>90,92%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>72,29%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>12859</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9844</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14095</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>91,23%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>69,84%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12297</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>34</t>
@@ -1824,27 +1824,27 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>24763</t>
+          <t>24835</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22101</t>
+          <t>22059</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26009</t>
+          <t>26071</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1862,107 +1862,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1246</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3800</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9,08%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4251</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>8,77%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>27,71%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>30,16%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4012</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1246</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3908</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>13713</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>13713</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>13713</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12297</t>
+          <t>14095</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12297</t>
+          <t>14095</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12297</t>
+          <t>14095</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>26009</t>
+          <t>26071</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>26009</t>
+          <t>26071</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>26009</t>
+          <t>26071</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>40269</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>36010</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>41558</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>96,18%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>86,01%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>37450</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>33489</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>40057</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>89,43%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>79,97%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>95,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>42688</t>
+          <t>35473</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38422</t>
+          <t>31567</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44091</t>
+          <t>37926</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>80137</t>
+          <t>75743</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75373</t>
+          <t>70902</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83490</t>
+          <t>78667</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5859</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>13,99%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>4428</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1821</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8389</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>10,57%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>20,03%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>8216</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>10751</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>41869</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>41869</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>41869</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>41878</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>41878</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>41878</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44477</t>
+          <t>39783</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44477</t>
+          <t>39783</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44477</t>
+          <t>39783</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>86354</t>
+          <t>81653</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>86354</t>
+          <t>81653</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>86354</t>
+          <t>81653</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
